--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk5pct_wu500000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk5pct_wu500000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>382581</t>
+          <t>202128</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>515176</t>
+          <t>313111</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>661069</t>
+          <t>348021</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>708787</t>
+          <t>360829</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>809838</t>
+          <t>449072</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>944981</t>
+          <t>495972</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1064145</t>
+          <t>568237</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1140666</t>
+          <t>572493</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1159579</t>
+          <t>587150</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1229188</t>
+          <t>642102</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1296585</t>
+          <t>654547</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1328338</t>
+          <t>673854</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1373165</t>
+          <t>699375</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1388460</t>
+          <t>689149</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1367719</t>
+          <t>678633</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1357128</t>
+          <t>678558</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
